--- a/SHINHWA_QMS_WORKFLOW/07_AUDIT/고객심사/SQ___________260930_SH_정식번호반영_연계정정_담당자확정.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/07_AUDIT/고객심사/SQ___________260930_SH_정식번호반영_연계정정_담당자확정.xlsx
@@ -29174,7 +29174,11 @@
           <t>품질팀</t>
         </is>
       </c>
-      <c r="K19" s="4" t="n"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>이광재</t>
+        </is>
+      </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
           <t>기존 절차 연계</t>
@@ -29193,7 +29197,7 @@
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>※재판정(본문대조) 확정(2026-09-22, 품질경영담당 일괄판단 — 부서 정식회신 없이 처리): 관련 기존 문서란 참고 ⚠현장 실제 서식과 반드시 대조 확인 필요(철호님 직접 확인 권장) | FM번호 재부여(2026-09-22, 확정 연계절차 기준): SH-FM-PRD-N03 → SH-FM-WI030-01</t>
+          <t>※재판정(본문대조) 확정(2026-09-22, 품질경영담당 일괄판단 — 부서 정식회신 없이 처리): 관련 기존 문서란 참고 ⚠현장 실제 서식과 반드시 대조 확인 필요(철호님 직접 확인 권장) | FM번호 재부여(2026-09-22, 확정 연계절차 기준): SH-FM-PRD-N03 → SH-FM-WI030-01 | [담당자 지정 2026-10-08, 사용자 확정] 이전 표기: 공란</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -63956,7 +63960,11 @@
           <t>품질팀</t>
         </is>
       </c>
-      <c r="I31" s="4" t="n"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>이광재</t>
+        </is>
+      </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
           <t>기존 절차 연계</t>

--- a/SHINHWA_QMS_WORKFLOW/07_AUDIT/고객심사/SQ___________260930_SH_정식번호반영_연계정정_담당자확정.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/07_AUDIT/고객심사/SQ___________260930_SH_정식번호반영_연계정정_담당자확정.xlsx
@@ -29480,7 +29480,11 @@
           <t>생산팀</t>
         </is>
       </c>
-      <c r="K23" s="4" t="n"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>이광재</t>
+        </is>
+      </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
           <t>기존 절차 연계</t>
@@ -29499,7 +29503,7 @@
       <c r="O23" s="4" t="n"/>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>※재판정(본문대조) 확정(2026-09-22, 품질경영담당 일괄판단 — 부서 정식회신 없이 처리): 관련 기존 문서란 참고 | FM번호 재부여(2026-09-22, 확정 연계절차 기준): SH-FM-WI001-01 → SH-FM-WI004-06</t>
+          <t>※재판정(본문대조) 확정(2026-09-22, 품질경영담당 일괄판단 — 부서 정식회신 없이 처리): 관련 기존 문서란 참고 | FM번호 재부여(2026-09-22, 확정 연계절차 기준): SH-FM-WI001-01 → SH-FM-WI004-06 | [담당자 지정 2026-10-08, 사용자 확정] 이전 표기: 공란</t>
         </is>
       </c>
       <c r="Q23" s="4" t="inlineStr">
@@ -63782,7 +63786,11 @@
           <t>생산팀</t>
         </is>
       </c>
-      <c r="I28" s="3" t="n"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>이광재</t>
+        </is>
+      </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
           <t>기존 절차 연계</t>
